--- a/tasks/finalpool/terminal-wc-howtocook-gform-excel-notion/groundtruth_workspace/Meal_Kit_Analysis.xlsx
+++ b/tasks/finalpool/terminal-wc-howtocook-gform-excel-notion/groundtruth_workspace/Meal_Kit_Analysis.xlsx
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
